--- a/xiuxian配置表/indir/z_xiaoguo_catalog.xlsx
+++ b/xiuxian配置表/indir/z_xiaoguo_catalog.xlsx
@@ -6961,7 +6961,7 @@
     <row r="200" ht="27" customHeight="1">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>tribulation_control</t>
+          <t>dujie_control</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
@@ -6993,7 +6993,7 @@
     <row r="201" ht="27" customHeight="1">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>tribulation_damage</t>
+          <t>dujie_damage</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
@@ -7025,7 +7025,7 @@
     <row r="202" ht="27" customHeight="1">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>tribulation_energy_absorption</t>
+          <t>dujie_energy_absorption</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
@@ -7057,7 +7057,7 @@
     <row r="203" ht="27" customHeight="1">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>tribulation_forecast</t>
+          <t>dujie_forecast</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
@@ -7089,7 +7089,7 @@
     <row r="204" ht="27" customHeight="1">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>tribulation_mark</t>
+          <t>dujie_mark</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
@@ -7121,7 +7121,7 @@
     <row r="205" ht="27" customHeight="1">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>tribulation_plan_slots</t>
+          <t>dujie_plan_slots</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
@@ -7153,7 +7153,7 @@
     <row r="206" ht="27" customHeight="1">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>tribulation_recovery</t>
+          <t>dujie_recovery</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
@@ -7185,7 +7185,7 @@
     <row r="207" ht="27" customHeight="1">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>tribulation_resistance</t>
+          <t>dujie_resistance</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
@@ -7217,7 +7217,7 @@
     <row r="208" ht="27" customHeight="1">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>tribulation_resource_efficiency</t>
+          <t>dujie_resource_efficiency</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="209" ht="27" customHeight="1">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>tribulation_sever</t>
+          <t>dujie_sever</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
@@ -7281,7 +7281,7 @@
     <row r="210" ht="27" customHeight="1">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>tribulation_warning_time</t>
+          <t>dujie_warning_time</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
@@ -7377,7 +7377,7 @@
     <row r="213" ht="27" customHeight="1">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>void_herb_growth</t>
+          <t>lianxu_herb_growth</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
@@ -7409,7 +7409,7 @@
     <row r="214" ht="27" customHeight="1">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>void_mobility</t>
+          <t>lianxu_mobility</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
@@ -7441,7 +7441,7 @@
     <row r="215" ht="27" customHeight="1">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>void_resistance</t>
+          <t>lianxu_resistance</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
@@ -7473,7 +7473,7 @@
     <row r="216" ht="27" customHeight="1">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>void_route_safety</t>
+          <t>lianxu_route_safety</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
@@ -7505,7 +7505,7 @@
     <row r="217" ht="27" customHeight="1">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>void_ship_range</t>
+          <t>lianxu_ship_range</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
@@ -7537,7 +7537,7 @@
     <row r="218" ht="27" customHeight="1">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>void_spell_accuracy</t>
+          <t>lianxu_spell_accuracy</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
@@ -7569,7 +7569,7 @@
     <row r="219" ht="27" customHeight="1">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>void_survival</t>
+          <t>lianxu_survival</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
@@ -7601,7 +7601,7 @@
     <row r="220" ht="27" customHeight="1">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>void_target_accuracy</t>
+          <t>lianxu_target_accuracy</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
@@ -7633,7 +7633,7 @@
     <row r="221" ht="27" customHeight="1">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>void_travel_speed</t>
+          <t>lianxu_travel_speed</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
